--- a/data-raw/InitialSpParamsMED.xlsx
+++ b/data-raw/InitialSpParamsMED.xlsx
@@ -310,7 +310,7 @@
     <t xml:space="preserve">Gsw_Toptim_Jarvis</t>
   </si>
   <si>
-    <t xml:space="preserve">Gsw_Tsens</t>
+    <t xml:space="preserve">Gsw_Tsens_Jarvis</t>
   </si>
   <si>
     <t xml:space="preserve">Gsw_AC_slope_Baldocchi</t>
@@ -2846,7 +2846,7 @@
     <tableColumn id="94" name="Gswmin"/>
     <tableColumn id="95" name="Gswmax"/>
     <tableColumn id="96" name="Gsw_Toptim_Jarvis"/>
-    <tableColumn id="97" name="Gsw_Tsens"/>
+    <tableColumn id="97" name="Gsw_Tsens_Jarvis"/>
     <tableColumn id="98" name="Gsw_AC_slope_Baldocchi"/>
     <tableColumn id="99" name="Gsw_P50_Baldocchi"/>
     <tableColumn id="100" name="Gsw_slope_Baldocchi"/>
